--- a/hisobotlar/Oqituvchilar royxati.xlsx
+++ b/hisobotlar/Oqituvchilar royxati.xlsx
@@ -461,21 +461,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -503,45 +506,60 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Pedagogik toifasi</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>Telefon raqami</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Tug'ilgan sanasi</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Tug'ilgan joyi</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Pasport seriya va raqami</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>JSHSHIR (PINFL)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>INN (STIR)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Plastik karta raqami</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Tamomlagan OTM / Ta'lim muassasasi</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>OTM tamomlagan yili</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Diplom bo'yicha mutaxassisligi</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Ishga kirgan buyruq sanasi</t>
         </is>
@@ -561,47 +579,58 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>+998 94 485 66 86</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>11.12.1986</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Kitob tumani</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>AD 6387297</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>31112862640255</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>531026980</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>9860080311188025</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Toshkent Pediatriya Tibbiyot instituti</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>16,06,2011</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Oliy hamshiralik ishi</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -621,47 +650,58 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>+998 91 470 39 64</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>11.02.1988</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>AE 4760879</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>31102882560109</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>521992768</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>9860080311251534</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiyasi</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>12.06.2010</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Oliy ma'lumotli hamshira</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -681,47 +721,58 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>+998 90 864 21 55</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>05.09.1957</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>AB 1389306</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>40509572560045</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>535156144</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>9860080311146577</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Samarqand davlat meditsina universiteti</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>28.06.1980</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Davolash</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -741,47 +792,54 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>+998 99 775 40 49</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>09.05.1988</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>AD 3879994</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>40905885590016</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>9860080311922456</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiyasi</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>14.06.2013</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Oliy ma'lumotli hamshira</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -801,47 +859,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>+998 91 961 03 04</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>20.09.1987</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Kitob tumani</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>AB 6572306</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>32009872640056</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Toshkent farmatsevtika instituti</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>10.06.2011</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>Biotexnalogiya</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -861,47 +922,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>+998 90 313 05 00</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>15.01.1998</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Kitob tumani</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>AE 3698603</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>41501985680018</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>O'zbekiston jahon tillari universiteti</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>28.06.2021</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>Ingliz tili va adabiyot o'qituvchisi</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -921,47 +985,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>+998 88 260 86 68</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>07.12.1989</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>AE 2829988</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>40712892560095</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Mirzo Ulug'bek nomidagi O'zbekiston Milliy universiteti</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>15.06.2012</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Biokimyo</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -981,47 +1048,58 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>+998 97 381 34 33</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>12.01.1987</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>AD 0594238</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>31201872730017</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>508274139</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>9860080311919635</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Mirzo Ulug'bek nomidagi O'zbekiston Milliy universiteti</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>16.06.2008</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>Falsafa</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -1041,47 +1119,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>+998 91 462 66 48</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>16.10.1988</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>AD 6227655</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>41610882560070</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiyasi</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>24.06.2010</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Oliy hamshiralik ishi</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -1101,47 +1182,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>+998 77 023 01 46</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>03.04.2001</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>AC 1298495</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>60304017890020</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiyasi</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
         <is>
           <t>15.06.2022</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>Oliy hamshiralik ishi</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -1161,47 +1245,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>+998 91 810 06 14</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>14.06.1999</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>AB 6147908</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>41406995590053</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiysi</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>15.06.2022</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Oliy ma'lumotli hamshira</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -1221,47 +1308,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>+998 88 589 29 21</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>22.04.1992</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>AE3796962</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>42204922560080</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiysi</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
         <is>
           <t>14.06.2017</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Oliy ma'lumotli hamshira</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -1281,47 +1371,50 @@
           <t>Asosiy o'qituvchilar</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>+998 88 564 14 41</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>14.07.1985</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Chiroqchi tumani</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>AB 7576700</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>41407852560095</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Toshkent farmatsevtika instituti</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>07.07.2009</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>Farmatsiya</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>28.08.2026</t>
         </is>
@@ -1341,47 +1434,54 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>+998 91 213 93 59</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>28.08.1981</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>AA 6393123</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>42808815590011</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>9860080311533196</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Toshkent Pediateriya tibbiyot instituti</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>06.06.2011</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>Oliy hamshiralik ishi</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1401,47 +1501,50 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>+998 90 517 05 15</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>11.11.1981</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Kitob tumani</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>AD 5571124</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>41111812640038</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Samarqand davlat tibbiyot instituti</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>27.06.2002</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Oliy ma'lumotli hamshira</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1461,47 +1564,50 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>+998 97 380 86 17</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>18.06.1976</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>AB 4848015</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>41806765590023</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Shahrisabz tibbiyot bilim yurti</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>.07.1994</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>Tibbiy hamshira</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1521,47 +1627,50 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>+998 88 854 87 97</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>18.04.1989</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>AD 8366544</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>31804892560060</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Samarqand davlat tibbiyot instituti</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>20.06.2014</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>Pediateriya ishi bo'yicha umumiy amaliyot vrach pediateri</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1581,47 +1690,50 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>+998 97 631 81 87</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>27.11.1987</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>AD 1713547</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>42711872560032</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Shahrisabz tibiyot kolleji</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>04.07.2007</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>Umumiy amaliyot hamshirasi</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1641,47 +1753,50 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>+998 91 636 35 98</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>27.11.1990</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>AB 9132346</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>42711902560072</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>ILM-U ZIYO BIZNES IBBIYOT TEXNIKUMI</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>17.07.1905</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>Hamshiralik ishi</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1701,47 +1816,50 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>+998 90 186 05 33</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>04.07.1985</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>AB 6655981</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>30407852530018</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Toshkent tibbiyot akademiyasi</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>20.06.2014</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>Umumiy amaliyot vrachi</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1761,47 +1879,58 @@
           <t>O'rindosh o'qituvchilar</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>+998 90 129 90 08</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>03.09.1995</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Qashqadaryo viloyati Kitob tumani</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>AE 2643207</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>40309952640064</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>598582343</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>9860080311393286</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>ALFRAGANUS UNIVERSITY</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>04.06.2026</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>Umumiy stomatolog shifokori</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
@@ -1809,7 +1938,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
